--- a/Data/wtryrtype.xlsx
+++ b/Data/wtryrtype.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cawater-my.sharepoint.com/personal/rosemary_hartman_water_ca_gov/Documents/salinity control gates/SMSCG/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{E82DFE74-879D-4857-B0A2-7C16A8805E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFCB478B-59A4-43CE-862E-B2D207CF5A99}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{E82DFE74-879D-4857-B0A2-7C16A8805E3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E84C71FB-46AD-4F40-8D9D-3CD302F9F1E7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{FFC84A21-9A32-4503-836D-92B86F6012D5}"/>
+    <workbookView xWindow="32160" yWindow="3360" windowWidth="21600" windowHeight="12525" xr2:uid="{FFC84A21-9A32-4503-836D-92B86F6012D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="11">
   <si>
     <t>WY</t>
   </si>
@@ -122,9 +122,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -162,7 +162,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -268,7 +268,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,7 +410,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285FF48E-1B64-4A88-8BF9-D3613EE5AE38}">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -2756,6 +2756,36 @@
         <v>6</v>
       </c>
     </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>2024</v>
+      </c>
+      <c r="E120">
+        <v>8.4</v>
+      </c>
+      <c r="F120" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>2025</v>
+      </c>
+      <c r="F121" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>2026</v>
+      </c>
+      <c r="E122">
+        <v>7.81</v>
+      </c>
+      <c r="F122" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
